--- a/public/templates/AHP_matrix_template.xlsx
+++ b/public/templates/AHP_matrix_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajeong/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ajeong/ahp-project-starter/AHP_frontend/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF59165-E717-C942-B1E2-56A5B3CEF209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DF7EB7-0B9C-E748-8BD5-449D5376FB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="25440" windowHeight="13100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,8 +124,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="Rectangle 1">
@@ -528,7 +528,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="Rectangle 1">
@@ -1208,10 +1208,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1219,13 +1219,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1233,10 +1233,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
